--- a/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,72</t>
+          <t>-1,54; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,94</t>
+          <t>-5,89; 2,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 9,53</t>
+          <t>-1,16; 9,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,0</t>
+          <t>-5,57; -0,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,31</t>
+          <t>-3,17; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,45</t>
+          <t>-3,08; 4,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 486,6</t>
+          <t>-85,16; 519,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 460,43</t>
+          <t>-84,04; 467,48</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,81</t>
+          <t>-4,61; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,0</t>
+          <t>-4,13; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,84</t>
+          <t>-1,61; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -1,8</t>
+          <t>-10,26; -1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,43</t>
+          <t>-2,19; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,67</t>
+          <t>-6,84; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,19</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 209,98</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,02</t>
+          <t>-3,46; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,45</t>
+          <t>-1,89; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,12</t>
+          <t>-1,87; 2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 9,42</t>
+          <t>-82,53; 23,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 181,96</t>
+          <t>-71,67; 146,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 132,93</t>
+          <t>-55,8; 140,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 7,8</t>
+          <t>-1,22; 8,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,83</t>
+          <t>-6,71; 2,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,44</t>
+          <t>-1,2; 9,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -0,08</t>
+          <t>-4,87; 0,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,97</t>
+          <t>-3,63; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 4,13</t>
+          <t>-2,41; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,16; 519,22</t>
+          <t>-100,0; 526,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 467,48</t>
+          <t>-70,46; 706,53</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,3</t>
+          <t>-4,54; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,0</t>
+          <t>-4,02; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,55</t>
+          <t>-1,62; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -1,63</t>
+          <t>-10,28; -1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,22</t>
+          <t>-2,18; 4,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,89</t>
+          <t>-6,95; 1,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; -1,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 209,98</t>
+          <t>-100,0; 158,84</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,11</t>
+          <t>-3,56; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,91; 1,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,01</t>
+          <t>-1,69; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 23,01</t>
+          <t>-85,52; 16,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 146,77</t>
+          <t>-70,99; 159,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 140,39</t>
+          <t>-54,12; 165,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,19</t>
+          <t>-1,27; 7,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,55</t>
+          <t>-5,63; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 9,27</t>
+          <t>-1,12; 9,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,36</t>
+          <t>-5,48; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,46</t>
+          <t>-2,95; 3,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,67</t>
+          <t>-2,97; 4,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 526,76</t>
+          <t>-82,63; 486,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,46; 706,53</t>
+          <t>-82,69; 460,43</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,64</t>
+          <t>-4,64; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,0</t>
+          <t>-4,62; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,75</t>
+          <t>-1,61; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -1,49</t>
+          <t>-10,47; -1,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,39</t>
+          <t>-2,11; 4,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,98</t>
+          <t>-7,42; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,13</t>
+          <t>-100,0; -16,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,84</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,19</t>
+          <t>-3,62; 0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,53</t>
+          <t>-1,81; 1,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,15</t>
+          <t>-1,86; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 16,02</t>
+          <t>-83,86; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 159,07</t>
+          <t>-69,87; 181,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 165,96</t>
+          <t>-58,11; 132,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,147 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>158,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-30,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>242,91%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.441705735109608</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7870570659121321</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.800994437773177</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1.589333565440642</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3041567543214855</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2.429117940754003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,27; 7,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 2,94</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 9,53</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.270335682349539</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.62727538644701</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.123505907608678</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.717451076400089</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.936982299322498</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.525409333401639</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-78,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,48; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,95; 3,31</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,97; 4,45</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-82,63; 486,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-82,69; 460,43</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.908306649242871</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.01089792390553401</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6464532558981394</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.783720914490479</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.004613811172022383</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2665455253020579</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-59,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.475724449677814</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.949486633569445</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.968945533973006</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.8263404601329019</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8269226973610904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 1,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,61; 2,84</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.30641775977046</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.452508214673625</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>4.866043571219546</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.604284160837879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +751,223 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-88,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-47,78%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.364945663824423</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.8260732599748126</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.09498515747066796</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.599084271254641</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1189056703255423</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,47; -1,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 4,43</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,42; 1,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -16,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.644803367252424</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.624812772208442</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.610139936998285</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.806606794795913</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.84016879073973</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.225596993896227</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4581306441852291</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.118875043901631</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.8820358126401247</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3199716587466765</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.477844776312335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.46839486939827</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.11166462515136</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.415714041936533</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-1.797369503161277</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.428333998234941</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.671524009591717</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.1619133118236923</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-54,52%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 1,45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 2,12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-83,86; 9,42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-69,87; 181,96</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-58,11; 132,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.671419679464448</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1938696565544074</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1283082115822249</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.545203008732238</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1062768404491198</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.05305336910917367</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.617815544654816</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.808478617752896</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.858607911069198</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.8385625379426065</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6986507045858715</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5810627472797583</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.01866911455452469</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.446720939344781</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.122949803087668</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.09421649981187356</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.819562085037443</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.32929966705838</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +976,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
